--- a/tests/fixtures/out/export_engine_samemerge.xlsx
+++ b/tests/fixtures/out/export_engine_samemerge.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>region</t>
   </si>
@@ -393,9 +393,6 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
       <c r="B5">
         <v>40</v>
       </c>
@@ -409,8 +406,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
